--- a/Hoadon/HDRa/1/3502386218_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDRa/1/3502386218_HDDienTuMayTinhTien.xlsx
@@ -302,6 +302,1612 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H7" s="7"/>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Hoàng Thảo Nghi</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>480 nguyễn tri phương quận 10 TPHCM</t>
+        </is>
+      </c>
+      <c r="K7" s="6"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O7" s="13" t="n">
+        <v>4900000.0</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H8" s="7"/>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Đăng Vinh</t>
+        </is>
+      </c>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O8" s="13" t="n">
+        <v>1099000.0</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Trần Ngọc Như Ý</t>
+        </is>
+      </c>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O9" s="13" t="n">
+        <v>1499000.0</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Quang Bình</t>
+        </is>
+      </c>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O10" s="13" t="n">
+        <v>1099000.0</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H11" s="7"/>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Nga</t>
+        </is>
+      </c>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="13" t="n">
+        <v>3781000.0</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Võ Trần Thực Hiên</t>
+        </is>
+      </c>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O12" s="13" t="n">
+        <v>5190000.0</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H13" s="7"/>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Thị Ánh Ngọc</t>
+        </is>
+      </c>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O13" s="13" t="n">
+        <v>3.12E7</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H14" s="7"/>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Kiều Hà Phương</t>
+        </is>
+      </c>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O14" s="13" t="n">
+        <v>1375000.0</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H15" s="7"/>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Bùi Thị Thanh Hương</t>
+        </is>
+      </c>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O15" s="13" t="n">
+        <v>3781000.0</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H16" s="7"/>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Bùi Thị Thanh Hương</t>
+        </is>
+      </c>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H17" s="7"/>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Hà Vy</t>
+        </is>
+      </c>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O17" s="13" t="n">
+        <v>4190000.0</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H18" s="7"/>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Lê Trần Ánh Dương</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Ô39, TDC 05, Đường D37, KDC Viet-Sing, phường An Phú, TP. Thuận An, Bình Dương</t>
+        </is>
+      </c>
+      <c r="K18" s="6"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="13" t="n">
+        <v>1100000.0</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H19" s="7"/>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Huỳnh Nguyễn Minh Thi</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>254D3 Đoàn Hoàng Minh phường Sơn Đông tỉnh Vĩnh Long</t>
+        </is>
+      </c>
+      <c r="K19" s="6"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="13" t="n">
+        <v>4190000.0</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H20" s="7"/>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Đào Khánh Hoàng</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Số 01, Tổ 13B, Khu Quang Trung 4, Phường Uông Bí, tỉnh Quảng Ninh</t>
+        </is>
+      </c>
+      <c r="K20" s="6"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="13" t="n">
+        <v>4990000.0</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H21" s="7"/>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Trần Hoàng Anh Cao</t>
+        </is>
+      </c>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O21" s="13" t="n">
+        <v>1099000.0</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H22" s="7"/>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Võ Thị Hồng Hạnh</t>
+        </is>
+      </c>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O22" s="13" t="n">
+        <v>1099000.0</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H23" s="7"/>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Linh</t>
+        </is>
+      </c>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O23" s="13" t="n">
+        <v>6400000.0</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H24" s="7"/>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Lê Liêu Tùng</t>
+        </is>
+      </c>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O24" s="13" t="n">
+        <v>4725000.0</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H25" s="7"/>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>Ngô Phương Chi</t>
+        </is>
+      </c>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O25" s="13" t="n">
+        <v>4725000.0</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H26" s="7"/>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Hoàng Phúc</t>
+        </is>
+      </c>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O26" s="13" t="n">
+        <v>4725000.0</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H27" s="7"/>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>Trần Chi Lê</t>
+        </is>
+      </c>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O27" s="13" t="n">
+        <v>3580000.0</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H28" s="7"/>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>Lê Minh Thư</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>Chung cư Florita đường d4 phường tân hưng quận 7, TP.HCM</t>
+        </is>
+      </c>
+      <c r="K28" s="6"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O28" s="13" t="n">
+        <v>4190000.0</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H29" s="7"/>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>Trần Thị Sơn</t>
+        </is>
+      </c>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O29" s="13" t="n">
+        <v>1230000.0</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H30" s="7"/>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>Trần Ánh Tuyết</t>
+        </is>
+      </c>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O30" s="13" t="n">
+        <v>3100000.0</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H31" s="7"/>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>Trương Võ Thiên Hương</t>
+        </is>
+      </c>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O31" s="13" t="n">
+        <v>1099000.0</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>C26MAA</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="H32" s="7"/>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>Đỗ Thị Mỹ Duyên</t>
+        </is>
+      </c>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O32" s="13" t="n">
+        <v>4740500.0</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:Q3"/>
